--- a/www/flightdata/xlsx/eoss-323.xlsx
+++ b/www/flightdata/xlsx/eoss-323.xlsx
@@ -2841,7 +2841,7 @@
         <v>20625.82</v>
       </c>
       <c r="I2">
-        <v>457</v>
+        <v>337</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
